--- a/Controller/IRESGController/Table_Result.xlsx
+++ b/Controller/IRESGController/Table_Result.xlsx
@@ -31,13 +31,13 @@
     <t xml:space="preserve">MS-COCO</t>
   </si>
   <si>
-    <t xml:space="preserve">R@10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R@20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R@50</t>
+    <t xml:space="preserve">Acc@10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acc@20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acc@50</t>
   </si>
   <si>
     <t xml:space="preserve">CLIP (ViT-B-32)</t>
@@ -70,6 +70,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -91,6 +92,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -99,12 +101,14 @@
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -149,12 +153,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -170,7 +174,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -192,7 +200,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.93"/>
   </cols>
@@ -294,17 +302,17 @@
       <c r="J4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5"/>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="6" t="n">
         <v>0.42695</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="6" t="n">
         <v>0.58745</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="6" t="n">
         <v>0.76955</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -374,17 +382,17 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="5"/>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="6" t="n">
         <v>0.4249</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="6" t="n">
         <v>0.58539</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="6" t="n">
         <v>0.768</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -804,12 +812,7 @@
     <mergeCell ref="B6:B8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="R@10"/>
-    <hyperlink ref="D2" r:id="rId2" display="R@20"/>
-    <hyperlink ref="E2" r:id="rId3" display="R@50"/>
-    <hyperlink ref="F2" r:id="rId4" display="R@10"/>
-    <hyperlink ref="G2" r:id="rId5" display="R@20"/>
-    <hyperlink ref="H2" r:id="rId6" display="R@50"/>
+    <hyperlink ref="E2" r:id="rId1" display="Acc@50"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/Controller/IRESGController/Table_Result.xlsx
+++ b/Controller/IRESGController/Table_Result.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
   <si>
     <t xml:space="preserve">Methods </t>
   </si>
@@ -46,13 +46,13 @@
     <t xml:space="preserve">Non-Editted</t>
   </si>
   <si>
+    <t xml:space="preserve">CLIP (ViT-L-14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propose</t>
+  </si>
+  <si>
     <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIP (ViT-L-14)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propose</t>
   </si>
   <si>
     <t xml:space="preserve">Editted</t>
@@ -200,7 +200,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.93"/>
   </cols>
@@ -263,21 +263,21 @@
       <c r="E3" s="2" t="n">
         <v>0.52469</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>8</v>
+      <c r="F3" s="2" t="n">
+        <v>0.09848</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.31305</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="2" t="n">
@@ -289,21 +289,21 @@
       <c r="E4" s="2" t="n">
         <v>0.51955</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>8</v>
+      <c r="F4" s="2" t="n">
+        <v>0.09702</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.17009</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.32893</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="6" t="n">
@@ -316,13 +316,13 @@
         <v>0.76955</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="3"/>
@@ -343,21 +343,21 @@
       <c r="E6" s="2" t="n">
         <v>0.55761</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>8</v>
+      <c r="F6" s="2" t="n">
+        <v>0.10215</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.16764</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.32991</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="2" t="n">
@@ -369,21 +369,21 @@
       <c r="E7" s="2" t="n">
         <v>0.55864</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>8</v>
+      <c r="F7" s="2" t="n">
+        <v>0.10411</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.18377</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.34971</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="6" t="n">
@@ -396,13 +396,13 @@
         <v>0.768</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="3"/>

--- a/Controller/IRESGController/Table_Result.xlsx
+++ b/Controller/IRESGController/Table_Result.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="25">
   <si>
     <t xml:space="preserve">Methods </t>
   </si>
@@ -56,6 +57,111 @@
   </si>
   <si>
     <t xml:space="preserve">Editted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recall@10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Recall</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">@20</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Recall@50</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Recall</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">@10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Recall</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">@50</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Scene Graph Matching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VSE-SG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qwen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ResNet50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross</t>
   </si>
 </sst>
 </file>
@@ -65,7 +171,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -104,6 +210,22 @@
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
       <i val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -153,7 +275,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -182,6 +304,22 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -200,7 +338,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.93"/>
   </cols>
@@ -822,4 +960,438 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="2" t="n">
+        <v>0.18827</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.52469</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.09848</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.31305</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="2" t="n">
+        <v>0.17284</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.29167</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.51955</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.09702</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.17009</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.32893</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="6" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.58539</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>0.8089</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>0.92058</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>0.98558</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6" t="n">
+        <v>0.42695</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.58745</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.76955</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>0.48778</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>0.82625</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="B3:B9"/>
+    <mergeCell ref="B10:B15"/>
+    <mergeCell ref="B16:B19"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="Recall@50"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/Controller/IRESGController/Table_Result.xlsx
+++ b/Controller/IRESGController/Table_Result.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="26">
   <si>
     <t xml:space="preserve">Methods </t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t xml:space="preserve">Image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLIP2</t>
   </si>
   <si>
     <t xml:space="preserve">Cross</t>
@@ -275,7 +278,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -312,11 +315,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -967,7 +978,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.72"/>
@@ -1015,7 +1026,7 @@
       <c r="A3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="9" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -1041,7 +1052,7 @@
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="2" t="n">
         <v>0.18827</v>
       </c>
@@ -1065,7 +1076,7 @@
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="9"/>
       <c r="C5" s="2" t="n">
         <v>0.17284</v>
       </c>
@@ -1089,7 +1100,7 @@
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="9"/>
       <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
@@ -1113,31 +1124,55 @@
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="2" t="n">
+        <v>0.00617</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.01132</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.02675</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.00367</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.00635</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.01271</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="9"/>
       <c r="C9" s="6" t="n">
         <v>0.4249</v>
       </c>
@@ -1147,13 +1182,13 @@
       <c r="E9" s="6" t="n">
         <v>0.768</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="10" t="n">
         <v>0.8089</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="10" t="n">
         <v>0.92058</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="10" t="n">
         <v>0.98558</v>
       </c>
     </row>
@@ -1161,7 +1196,7 @@
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="9" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1187,102 +1222,127 @@
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>10</v>
+      <c r="B11" s="9"/>
+      <c r="C11" s="2" t="n">
+        <v>0.20988</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.55761</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.10215</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0.16764</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0.32991</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>10</v>
+      <c r="B12" s="9"/>
+      <c r="C12" s="2" t="n">
+        <v>0.19959</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.55864</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.10411</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.18377</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.34971</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="2" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.60905</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.24536</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0.50269</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="2" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.43673</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0.58899</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.21285</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0.46848</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="B15" s="9"/>
+      <c r="C15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="B16" s="9"/>
       <c r="C16" s="2" t="s">
         <v>10</v>
       </c>
@@ -1303,10 +1363,10 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="6"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="12" t="s">
+        <v>25</v>
+      </c>
       <c r="C17" s="2" t="s">
         <v>10</v>
       </c>
@@ -1328,49 +1388,73 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="12"/>
+      <c r="C18" s="2" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.49949</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0.66307</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0.26393</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0.54497</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="B19" s="12"/>
+      <c r="C19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6" t="n">
+      <c r="B20" s="12"/>
+      <c r="C20" s="6" t="n">
         <v>0.42695</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D20" s="6" t="n">
         <v>0.58745</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E20" s="6" t="n">
         <v>0.76955</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F20" s="10" t="n">
         <v>0.48778</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G20" s="10" t="n">
         <v>0.652</v>
       </c>
-      <c r="H19" s="9" t="n">
+      <c r="H20" s="10" t="n">
         <v>0.82625</v>
       </c>
     </row>
@@ -1380,8 +1464,8 @@
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="B3:B9"/>
-    <mergeCell ref="B10:B15"/>
-    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="B10:B16"/>
+    <mergeCell ref="B17:B20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="Recall@50"/>

--- a/Controller/IRESGController/Table_Result.xlsx
+++ b/Controller/IRESGController/Table_Result.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="26">
   <si>
     <t xml:space="preserve">Methods </t>
   </si>
@@ -62,84 +63,12 @@
     <t xml:space="preserve">Recall@10</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Recall</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">@20</t>
-    </r>
+    <t xml:space="preserve">Recall@20</t>
   </si>
   <si>
     <t xml:space="preserve">Recall@50</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Recall</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">@10</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Recall</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">@50</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Scene Graph Matching</t>
   </si>
   <si>
@@ -165,6 +94,12 @@
   </si>
   <si>
     <t xml:space="preserve">Cross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Answer</t>
   </si>
 </sst>
 </file>
@@ -174,7 +109,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -218,14 +153,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <i val="true"/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -278,7 +205,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -307,15 +234,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -325,10 +248,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -349,7 +268,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.93"/>
   </cols>
@@ -979,9 +898,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1006,28 +925,28 @@
       <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
@@ -1052,7 +971,7 @@
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="9"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="2" t="n">
         <v>0.18827</v>
       </c>
@@ -1076,7 +995,7 @@
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="9"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="2" t="n">
         <v>0.17284</v>
       </c>
@@ -1098,9 +1017,9 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="9"/>
+        <v>17</v>
+      </c>
+      <c r="B6" s="8"/>
       <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
@@ -1122,9 +1041,9 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="9"/>
+        <v>18</v>
+      </c>
+      <c r="B7" s="8"/>
       <c r="C7" s="2" t="n">
         <v>0.00617</v>
       </c>
@@ -1146,9 +1065,9 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="9"/>
+        <v>19</v>
+      </c>
+      <c r="B8" s="8"/>
       <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
@@ -1172,7 +1091,7 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="9"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="6" t="n">
         <v>0.4249</v>
       </c>
@@ -1182,22 +1101,22 @@
       <c r="E9" s="6" t="n">
         <v>0.768</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="9" t="n">
         <v>0.8089</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="9" t="n">
         <v>0.92058</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H9" s="9" t="n">
         <v>0.98558</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>10</v>
@@ -1222,7 +1141,7 @@
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="9"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="2" t="n">
         <v>0.20988</v>
       </c>
@@ -1246,7 +1165,7 @@
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="9"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="2" t="n">
         <v>0.19959</v>
       </c>
@@ -1268,9 +1187,9 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="9"/>
+        <v>18</v>
+      </c>
+      <c r="B13" s="8"/>
       <c r="C13" s="2" t="n">
         <v>0.33436</v>
       </c>
@@ -1292,9 +1211,9 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="9"/>
+        <v>22</v>
+      </c>
+      <c r="B14" s="8"/>
       <c r="C14" s="2" t="n">
         <v>0.31276</v>
       </c>
@@ -1316,9 +1235,9 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="9"/>
+        <v>19</v>
+      </c>
+      <c r="B15" s="8"/>
       <c r="C15" s="2" t="s">
         <v>10</v>
       </c>
@@ -1342,30 +1261,30 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>10</v>
+      <c r="B16" s="8"/>
+      <c r="C16" s="6" t="n">
+        <v>0.54784</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.70936</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0.86934</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.50709</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.66398</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.83529</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12" t="s">
-        <v>25</v>
+      <c r="A17" s="10"/>
+      <c r="B17" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>10</v>
@@ -1388,9 +1307,9 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="B18" s="8"/>
       <c r="C18" s="2" t="n">
         <v>0.38169</v>
       </c>
@@ -1412,9 +1331,9 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="12"/>
+        <v>19</v>
+      </c>
+      <c r="B19" s="8"/>
       <c r="C19" s="2" t="s">
         <v>10</v>
       </c>
@@ -1438,7 +1357,7 @@
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="12"/>
+      <c r="B20" s="8"/>
       <c r="C20" s="6" t="n">
         <v>0.42695</v>
       </c>
@@ -1448,13 +1367,13 @@
       <c r="E20" s="6" t="n">
         <v>0.76955</v>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="9" t="n">
         <v>0.48778</v>
       </c>
-      <c r="G20" s="10" t="n">
+      <c r="G20" s="9" t="n">
         <v>0.652</v>
       </c>
-      <c r="H20" s="10" t="n">
+      <c r="H20" s="9" t="n">
         <v>0.82625</v>
       </c>
     </row>
@@ -1467,9 +1386,37 @@
     <mergeCell ref="B10:B16"/>
     <mergeCell ref="B17:B20"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" display="Recall@50"/>
-  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="66.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="86"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/Controller/IRESGController/Table_Result.xlsx
+++ b/Controller/IRESGController/Table_Result.xlsx
@@ -9,8 +9,9 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="26">
   <si>
     <t xml:space="preserve">Methods </t>
   </si>
@@ -171,12 +172,75 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -205,7 +269,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -234,20 +298,68 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -268,7 +380,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.93"/>
   </cols>
@@ -897,495 +1009,9 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.71"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="2" t="n">
-        <v>0.18827</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.30813</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.52469</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.09848</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.1586</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0.31305</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="2" t="n">
-        <v>0.17284</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.29167</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.51955</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.09702</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.17009</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0.32893</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="2" t="n">
-        <v>0.00617</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0.01132</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0.02675</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.00367</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0.00635</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0.01271</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="6" t="n">
-        <v>0.4249</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>0.58539</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>0.8089</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>0.92058</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>0.98558</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="2" t="n">
-        <v>0.20988</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>0.33436</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>0.55761</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0.10215</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>0.16764</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0.32991</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="2" t="n">
-        <v>0.19959</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>0.32613</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>0.55864</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0.10411</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>0.18377</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>0.34971</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="2" t="n">
-        <v>0.33436</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>0.4501</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0.60905</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0.24536</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>0.34555</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>0.50269</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="2" t="n">
-        <v>0.31276</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>0.43673</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0.58899</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.21285</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0.30303</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0.46848</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="6" t="n">
-        <v>0.54784</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>0.70936</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>0.86934</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>0.50709</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>0.66398</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>0.83529</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="2" t="n">
-        <v>0.38169</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>0.49949</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>0.66307</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>0.26393</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>0.37048</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>0.54497</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="6" t="n">
-        <v>0.42695</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>0.58745</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>0.76955</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>0.48778</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="H20" s="9" t="n">
-        <v>0.82625</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B3:B9"/>
-    <mergeCell ref="B10:B16"/>
-    <mergeCell ref="B17:B20"/>
-  </mergeCells>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1401,8 +1027,504 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B1:I21"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.71"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="7"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="2" t="n">
+        <v>0.18827</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>0.52469</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.09848</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>0.31305</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="2" t="n">
+        <v>0.17284</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.29167</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0.51955</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.09702</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.17009</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>0.32893</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="2" t="n">
+        <v>0.00617</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.01132</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.02675</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.00367</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.00635</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>0.01271</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="18" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>0.58539</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>0.52058</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>0.58558</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="2" t="n">
+        <v>0.20988</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.55761</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.10215</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.16764</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>0.32991</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="2" t="n">
+        <v>0.19959</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>0.55864</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0.10411</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0.18377</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <v>0.34971</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="2" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>0.60905</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0.24536</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="I14" s="16" t="n">
+        <v>0.50269</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="2" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0.43673</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>0.58899</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0.21285</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="I15" s="16" t="n">
+        <v>0.46848</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="D17" s="18" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>0.50936</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>0.66934</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>0.63529</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0.49949</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>0.66307</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0.26393</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="I18" s="16" t="n">
+        <v>0.54497</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="18" t="n">
+        <v>0.52695</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>0.68745</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>0.86955</v>
+      </c>
+      <c r="G20" s="20" t="n">
+        <v>0.58778</v>
+      </c>
+      <c r="H20" s="20" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="I20" s="21" t="n">
+        <v>0.82625</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C21" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="C4:C10"/>
+    <mergeCell ref="C11:C17"/>
+    <mergeCell ref="C18:C20"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="66.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="86"/>

--- a/Controller/IRESGController/Table_Result.xlsx
+++ b/Controller/IRESGController/Table_Result.xlsx
@@ -1162,13 +1162,13 @@
         <v>0.63529</v>
       </c>
       <c r="F16" s="1" t="str">
-        <v>0.14729</v>
+        <v>0.13726</v>
       </c>
       <c r="G16" s="1" t="str">
-        <v>0.1694</v>
+        <v>0.15817</v>
       </c>
       <c r="H16" s="1" t="str">
-        <v>0.18772</v>
+        <v>0.17841</v>
       </c>
     </row>
     <row r="17">
